--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -49900,7 +49900,7 @@
         <v>133486102</v>
       </c>
       <c r="B438" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6462,7 +6462,7 @@
         <v>136994798</v>
       </c>
       <c r="B55" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>136994785</v>
       </c>
       <c r="B63" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>136969540</v>
       </c>
       <c r="B88" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>136969547</v>
       </c>
       <c r="B89" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>136994770</v>
       </c>
       <c r="B90" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>136994742</v>
       </c>
       <c r="B547" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>136994755</v>
       </c>
       <c r="B548" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>136994801</v>
       </c>
       <c r="B549" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63349,7 +63349,7 @@
         <v>136994733</v>
       </c>
       <c r="B552" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>136994767</v>
       </c>
       <c r="B553" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63583,7 +63583,7 @@
         <v>136994769</v>
       </c>
       <c r="B554" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>136994789</v>
       </c>
       <c r="B555" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>136994781</v>
       </c>
       <c r="B567" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>136969546</v>
       </c>
       <c r="B593" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6462,7 +6462,7 @@
         <v>136994798</v>
       </c>
       <c r="B55" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>136994785</v>
       </c>
       <c r="B63" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>136969540</v>
       </c>
       <c r="B88" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>136969547</v>
       </c>
       <c r="B89" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>136994770</v>
       </c>
       <c r="B90" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>136994742</v>
       </c>
       <c r="B547" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>136994755</v>
       </c>
       <c r="B548" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>136994801</v>
       </c>
       <c r="B549" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63349,7 +63349,7 @@
         <v>136994733</v>
       </c>
       <c r="B552" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>136994767</v>
       </c>
       <c r="B553" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63583,7 +63583,7 @@
         <v>136994769</v>
       </c>
       <c r="B554" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>136994789</v>
       </c>
       <c r="B555" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>136994781</v>
       </c>
       <c r="B567" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>136969546</v>
       </c>
       <c r="B593" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6462,7 +6462,7 @@
         <v>136994798</v>
       </c>
       <c r="B55" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>136994785</v>
       </c>
       <c r="B63" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>136969540</v>
       </c>
       <c r="B88" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>136969547</v>
       </c>
       <c r="B89" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>136994770</v>
       </c>
       <c r="B90" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>136994742</v>
       </c>
       <c r="B547" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>136994755</v>
       </c>
       <c r="B548" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>136994801</v>
       </c>
       <c r="B549" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63349,7 +63349,7 @@
         <v>136994733</v>
       </c>
       <c r="B552" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>136994767</v>
       </c>
       <c r="B553" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63583,7 +63583,7 @@
         <v>136994769</v>
       </c>
       <c r="B554" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>136994789</v>
       </c>
       <c r="B555" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>136994781</v>
       </c>
       <c r="B567" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>136969546</v>
       </c>
       <c r="B593" t="n">
-        <v>92508</v>
+        <v>92509</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68323,7 +68323,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92509</v>
+        <v>92515</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68323,7 +68323,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92515</v>
+        <v>92519</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68323,7 +68323,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92519</v>
+        <v>92521</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>136969539</v>
       </c>
       <c r="B312" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>136969548</v>
       </c>
       <c r="B313" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>136994749</v>
       </c>
       <c r="B314" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>136994750</v>
       </c>
       <c r="B315" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>136994722</v>
       </c>
       <c r="B369" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>136994761</v>
       </c>
       <c r="B370" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>136994763</v>
       </c>
       <c r="B371" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>136994764</v>
       </c>
       <c r="B372" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>136994792</v>
       </c>
       <c r="B373" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>136994797</v>
       </c>
       <c r="B374" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -51830,7 +51830,7 @@
         <v>133486102</v>
       </c>
       <c r="B454" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -51956,7 +51956,7 @@
         <v>136969542</v>
       </c>
       <c r="B455" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>136994799</v>
       </c>
       <c r="B456" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>136994730</v>
       </c>
       <c r="B517" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68323,7 +68323,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92521</v>
+        <v>92534</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>136969539</v>
       </c>
       <c r="B312" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>136969548</v>
       </c>
       <c r="B313" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>136994749</v>
       </c>
       <c r="B314" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>136994750</v>
       </c>
       <c r="B315" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>136994722</v>
       </c>
       <c r="B369" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>136994761</v>
       </c>
       <c r="B370" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>136994763</v>
       </c>
       <c r="B371" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>136994764</v>
       </c>
       <c r="B372" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>136994792</v>
       </c>
       <c r="B373" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>136994797</v>
       </c>
       <c r="B374" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -51830,7 +51830,7 @@
         <v>133486102</v>
       </c>
       <c r="B454" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -51956,7 +51956,7 @@
         <v>136969542</v>
       </c>
       <c r="B455" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>136994799</v>
       </c>
       <c r="B456" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>136994730</v>
       </c>
       <c r="B517" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68323,7 +68323,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -34679,11 +34679,7 @@
       <c r="I312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
@@ -34799,11 +34795,7 @@
       <c r="I313" t="inlineStr"/>
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
@@ -34924,11 +34916,7 @@
       <c r="I314" t="inlineStr"/>
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
@@ -35053,11 +35041,7 @@
       </c>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
@@ -41852,11 +41836,7 @@
       <c r="I373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr"/>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr"/>
       <c r="P373" t="inlineStr">
         <is>
@@ -51860,11 +51840,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="M454" t="inlineStr"/>
       <c r="P454" t="inlineStr">
         <is>
           <t>Sjös Fäbod, Dlr</t>
@@ -51984,11 +51960,7 @@
       <c r="I455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M455" t="inlineStr"/>
       <c r="N455" t="inlineStr"/>
       <c r="P455" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106407</v>
+        <v>106411</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92536</v>
+        <v>92539</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>136969539</v>
       </c>
       <c r="B312" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>136969548</v>
       </c>
       <c r="B313" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>136994749</v>
       </c>
       <c r="B314" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>136994750</v>
       </c>
       <c r="B315" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>136994722</v>
       </c>
       <c r="B369" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>136994761</v>
       </c>
       <c r="B370" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>136994763</v>
       </c>
       <c r="B371" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136994764</v>
       </c>
       <c r="B372" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>136994792</v>
       </c>
       <c r="B373" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>136994797</v>
       </c>
       <c r="B374" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>136969542</v>
       </c>
       <c r="B455" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>136994799</v>
       </c>
       <c r="B456" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>136994730</v>
       </c>
       <c r="B517" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106411</v>
+        <v>106430</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92539</v>
+        <v>92549</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106430</v>
+        <v>106431</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>136969539</v>
       </c>
       <c r="B312" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>136969548</v>
       </c>
       <c r="B313" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>136994749</v>
       </c>
       <c r="B314" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>136994750</v>
       </c>
       <c r="B315" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>136994722</v>
       </c>
       <c r="B369" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>136994761</v>
       </c>
       <c r="B370" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>136994763</v>
       </c>
       <c r="B371" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136994764</v>
       </c>
       <c r="B372" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>136994792</v>
       </c>
       <c r="B373" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>136994797</v>
       </c>
       <c r="B374" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>136969542</v>
       </c>
       <c r="B455" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>136994799</v>
       </c>
       <c r="B456" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>136994730</v>
       </c>
       <c r="B517" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106431</v>
+        <v>106436</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106436</v>
+        <v>106439</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>136969539</v>
       </c>
       <c r="B312" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>136969548</v>
       </c>
       <c r="B313" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>136994749</v>
       </c>
       <c r="B314" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>136994750</v>
       </c>
       <c r="B315" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>136994722</v>
       </c>
       <c r="B369" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>136994761</v>
       </c>
       <c r="B370" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>136994763</v>
       </c>
       <c r="B371" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136994764</v>
       </c>
       <c r="B372" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>136994792</v>
       </c>
       <c r="B373" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>136994797</v>
       </c>
       <c r="B374" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -59222,7 +59222,7 @@
         <v>136994730</v>
       </c>
       <c r="B517" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106439</v>
+        <v>106445</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106445</v>
+        <v>106446</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106446</v>
+        <v>106458</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92560</v>
+        <v>92572</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106458</v>
+        <v>106459</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92572</v>
+        <v>92573</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6235,7 +6235,7 @@
         <v>136994721</v>
       </c>
       <c r="B53" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106459</v>
+        <v>106462</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2022 artfynd.xlsx
+++ b/artfynd/A 53849-2022 artfynd.xlsx
@@ -6578,7 +6578,7 @@
         <v>136994798</v>
       </c>
       <c r="B56" t="n">
-        <v>96646</v>
+        <v>96647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136994785</v>
       </c>
       <c r="B64" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136969540</v>
       </c>
       <c r="B89" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>136969547</v>
       </c>
       <c r="B90" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>136994770</v>
       </c>
       <c r="B91" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>136994742</v>
       </c>
       <c r="B548" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
         <v>136994755</v>
       </c>
       <c r="B549" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>136994801</v>
       </c>
       <c r="B550" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>136994733</v>
       </c>
       <c r="B553" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>136994767</v>
       </c>
       <c r="B554" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>136994769</v>
       </c>
       <c r="B555" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -63788,7 +63788,7 @@
         <v>136994789</v>
       </c>
       <c r="B556" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65228,7 +65228,7 @@
         <v>136994781</v>
       </c>
       <c r="B568" t="n">
-        <v>106462</v>
+        <v>106464</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>136969546</v>
       </c>
       <c r="B594" t="n">
-        <v>92576</v>
+        <v>92577</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
